--- a/public/data/New_Book.xlsx
+++ b/public/data/New_Book.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\jinsharnam\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\jinsharnammedia\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1479,18 +1479,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="43" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="136.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="136.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>93</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>1</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>9826395777</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -1541,7 +1541,7 @@
         <v>9822242791</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>95717004183</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>9829116369</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>9587220111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>7046341111</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>8890212345</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>9867756888</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>9460490960</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>20</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>9820134140</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>21</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>9810180510</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>22</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>9414056886</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>23</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>9425308720</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>24</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>9821228174</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>25</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>9414051102</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>26</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>9321135335</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>27</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>9826495777</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
         <v>28</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>9929050403</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>29</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>9610441111</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="13">
         <v>30</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>7838166822</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="13">
         <v>31</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>9301100201</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <v>32</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>9829019301</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="13">
         <v>33</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>9413180225</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="13">
         <v>34</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>9820402573</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>35</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
         <v>36</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>37</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>9825007333</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>38</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>9824403400</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>39</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>98241293358</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
         <v>40</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="13">
         <v>41</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>9414403681</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
         <v>42</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>9827031443</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>43</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>9811505425</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="13">
         <v>44</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>9820221166</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>45</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="13">
         <v>46</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9829064400</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="13">
         <v>47</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>9810061204</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="13">
         <v>48</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>9718930384</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="13">
         <v>49</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>9926246887</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="13">
         <v>50</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>9414737035</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="13">
         <v>51</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>8888111999</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="13">
         <v>52</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>8805002505</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="13">
         <v>53</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>9822056066</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="13">
         <v>54</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>9822094737</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="13">
         <v>55</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>9823023051</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="13">
         <v>56</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>98220273336</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="13">
         <v>57</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>9822242791</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="13">
         <v>58</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="13">
         <v>59</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>9425188995</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="13">
         <v>60</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>9828039084</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="13">
         <v>61</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>9822024177</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="13">
         <v>62</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>9831038670</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="13">
         <v>63</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>9414104567</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="13">
         <v>64</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>9413308480</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="13">
         <v>65</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="13">
         <v>66</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>9414164671</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="13">
         <v>67</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>9829266576</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="13">
         <v>68</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>9414156680</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="13">
         <v>69</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>9784534990</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="13">
         <v>70</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>9879548940</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="13">
         <v>71</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>9823057050</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="13">
         <v>72</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>9818030088</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="13">
         <v>73</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>9829044481</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="13">
         <v>74</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>7722238440</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="13">
         <v>75</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>9825010151</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="13">
         <v>76</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>9414102255</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="13">
         <v>77</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>9829043342</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="13">
         <v>78</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>9460490980</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="13">
         <v>79</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>9829266576</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="13">
         <v>80</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>9826707059</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="13">
         <v>81</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>9914059108</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="13">
         <v>82</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="13">
         <v>83</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>9893332654</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="13">
         <v>84</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="13">
         <v>85</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>9810341058</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="13">
         <v>86</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>9999997513</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="13">
         <v>87</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="13">
         <v>88</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>9303243347</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="13">
         <v>89</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>9001361050</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="13">
         <v>90</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="13">
         <v>91</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>9702579797</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="13">
         <v>92</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>9001361050</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="13">
         <v>93</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>9414101170</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="13">
         <v>94</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>9414101395</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="13">
         <v>95</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>9929319494</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="13">
         <v>96</v>
       </c>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E95" s="17"/>
     </row>
-    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="13">
         <v>97</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>9928085649</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="13">
         <v>98</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>9414103677</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="13">
         <v>99</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="13">
         <v>100</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>9823151716</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="13">
         <v>101</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>9423783830</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="13">
         <v>102</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>9373831100</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="13">
         <v>103</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="13">
         <v>104</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="13">
         <v>105</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>9413616585</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="13">
         <v>106</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>9833237000</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="13">
         <v>107</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>9210034703</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="13">
         <v>108</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>9910303992</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="13">
         <v>109</v>
       </c>
@@ -3327,7 +3327,7 @@
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="13">
         <v>110</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="13">
         <v>111</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="13">
         <v>112</v>
       </c>
@@ -3381,7 +3381,7 @@
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="13">
         <v>113</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="13">
         <v>114</v>
       </c>
@@ -3419,7 +3419,7 @@
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="13">
         <v>115</v>
       </c>
@@ -3437,7 +3437,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="13">
         <v>116</v>
       </c>
@@ -3457,7 +3457,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="13">
         <v>117</v>
       </c>
@@ -3477,7 +3477,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="13">
         <v>118</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="13">
         <v>119</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="13">
         <v>120</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>9425115248</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="13">
         <v>121</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="13">
         <v>122</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>9302106984</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="13">
         <v>123</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>9827031575</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="13">
         <v>124</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>9826936900</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="13">
         <v>125</v>
       </c>
@@ -3617,7 +3617,7 @@
         <v>9425109999</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="13">
         <v>126</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>9893229157</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="13">
         <v>127</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>9822034331</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="13">
         <v>128</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="13">
         <v>129</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>9822194024</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="13">
         <v>130</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="13">
         <v>131</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>9403007000</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="13">
         <v>132</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>9822056066</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="13">
         <v>133</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>9987111110</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="13">
         <v>134</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>7977381306</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="13">
         <v>135</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>9870425586</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="13">
         <v>136</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>9076700000</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="13">
         <v>137</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>9822027336</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="13">
         <v>138</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="13">
         <v>139</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>9820293905</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="13">
         <v>140</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>9323444441</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="13">
         <v>141</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>9820648647</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="13">
         <v>142</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>9820025899</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="13">
         <v>143</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>7021162267</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="13">
         <v>144</v>
       </c>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E143" s="15"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="13">
         <v>145</v>
       </c>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E144" s="15"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="13">
         <v>146</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>9825010151</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="13">
         <v>147</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>9825145827</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="13">
         <v>148</v>
       </c>
